--- a/artfynd/A 10968-2025 artfynd.xlsx
+++ b/artfynd/A 10968-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128473458</v>
       </c>
       <c r="B2" t="n">
-        <v>91356</v>
+        <v>91448</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>128473328</v>
       </c>
       <c r="B3" t="n">
-        <v>100633</v>
+        <v>100726</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>128473231</v>
       </c>
       <c r="B4" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>128473282</v>
       </c>
       <c r="B5" t="n">
-        <v>91356</v>
+        <v>91448</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>128472993</v>
       </c>
       <c r="B6" t="n">
-        <v>98499</v>
+        <v>98592</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>128473375</v>
       </c>
       <c r="B7" t="n">
-        <v>100633</v>
+        <v>100726</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>128473340</v>
       </c>
       <c r="B8" t="n">
-        <v>82873</v>
+        <v>82942</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 10968-2025 artfynd.xlsx
+++ b/artfynd/A 10968-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128473458</v>
       </c>
       <c r="B2" t="n">
-        <v>91448</v>
+        <v>91454</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>128473328</v>
       </c>
       <c r="B3" t="n">
-        <v>100726</v>
+        <v>100734</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>128473231</v>
       </c>
       <c r="B4" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>128473282</v>
       </c>
       <c r="B5" t="n">
-        <v>91448</v>
+        <v>91454</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>128472993</v>
       </c>
       <c r="B6" t="n">
-        <v>98592</v>
+        <v>98600</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>128473375</v>
       </c>
       <c r="B7" t="n">
-        <v>100726</v>
+        <v>100734</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>128473340</v>
       </c>
       <c r="B8" t="n">
-        <v>82942</v>
+        <v>82946</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 10968-2025 artfynd.xlsx
+++ b/artfynd/A 10968-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128473458</v>
       </c>
       <c r="B2" t="n">
-        <v>91454</v>
+        <v>91460</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>128473328</v>
       </c>
       <c r="B3" t="n">
-        <v>100734</v>
+        <v>100741</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>128473282</v>
       </c>
       <c r="B5" t="n">
-        <v>91454</v>
+        <v>91460</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>128472993</v>
       </c>
       <c r="B6" t="n">
-        <v>98600</v>
+        <v>98606</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>128473375</v>
       </c>
       <c r="B7" t="n">
-        <v>100734</v>
+        <v>100741</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 10968-2025 artfynd.xlsx
+++ b/artfynd/A 10968-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128473458</v>
       </c>
       <c r="B2" t="n">
-        <v>91460</v>
+        <v>91462</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>128473328</v>
       </c>
       <c r="B3" t="n">
-        <v>100741</v>
+        <v>100746</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>128473231</v>
       </c>
       <c r="B4" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>128473282</v>
       </c>
       <c r="B5" t="n">
-        <v>91460</v>
+        <v>91462</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>128472993</v>
       </c>
       <c r="B6" t="n">
-        <v>98606</v>
+        <v>98609</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>128473375</v>
       </c>
       <c r="B7" t="n">
-        <v>100741</v>
+        <v>100746</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>128473340</v>
       </c>
       <c r="B8" t="n">
-        <v>82946</v>
+        <v>82948</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 10968-2025 artfynd.xlsx
+++ b/artfynd/A 10968-2025 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>128473328</v>
       </c>
       <c r="B3" t="n">
-        <v>100746</v>
+        <v>100752</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>128472993</v>
       </c>
       <c r="B6" t="n">
-        <v>98609</v>
+        <v>98612</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>128473375</v>
       </c>
       <c r="B7" t="n">
-        <v>100746</v>
+        <v>100752</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 10968-2025 artfynd.xlsx
+++ b/artfynd/A 10968-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128473458</v>
       </c>
       <c r="B2" t="n">
-        <v>91462</v>
+        <v>91463</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>128473328</v>
       </c>
       <c r="B3" t="n">
-        <v>100752</v>
+        <v>100753</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>128473282</v>
       </c>
       <c r="B5" t="n">
-        <v>91462</v>
+        <v>91463</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>128472993</v>
       </c>
       <c r="B6" t="n">
-        <v>98612</v>
+        <v>98613</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>128473375</v>
       </c>
       <c r="B7" t="n">
-        <v>100752</v>
+        <v>100753</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 10968-2025 artfynd.xlsx
+++ b/artfynd/A 10968-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128473458</v>
       </c>
       <c r="B2" t="n">
-        <v>91463</v>
+        <v>91490</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>128473328</v>
       </c>
       <c r="B3" t="n">
-        <v>100753</v>
+        <v>100780</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>128473231</v>
       </c>
       <c r="B4" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>128473282</v>
       </c>
       <c r="B5" t="n">
-        <v>91463</v>
+        <v>91490</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>128472993</v>
       </c>
       <c r="B6" t="n">
-        <v>98613</v>
+        <v>98640</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>128473375</v>
       </c>
       <c r="B7" t="n">
-        <v>100753</v>
+        <v>100780</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>128473340</v>
       </c>
       <c r="B8" t="n">
-        <v>82948</v>
+        <v>82975</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 10968-2025 artfynd.xlsx
+++ b/artfynd/A 10968-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128473458</v>
       </c>
       <c r="B2" t="n">
-        <v>91490</v>
+        <v>91495</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>128473328</v>
       </c>
       <c r="B3" t="n">
-        <v>100780</v>
+        <v>100786</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>128473231</v>
       </c>
       <c r="B4" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>128473282</v>
       </c>
       <c r="B5" t="n">
-        <v>91490</v>
+        <v>91495</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>128472993</v>
       </c>
       <c r="B6" t="n">
-        <v>98640</v>
+        <v>98646</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>128473375</v>
       </c>
       <c r="B7" t="n">
-        <v>100780</v>
+        <v>100786</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>128473340</v>
       </c>
       <c r="B8" t="n">
-        <v>82975</v>
+        <v>82979</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 10968-2025 artfynd.xlsx
+++ b/artfynd/A 10968-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128473458</v>
       </c>
       <c r="B2" t="n">
-        <v>91495</v>
+        <v>91500</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>128473328</v>
       </c>
       <c r="B3" t="n">
-        <v>100786</v>
+        <v>100793</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>128473282</v>
       </c>
       <c r="B5" t="n">
-        <v>91495</v>
+        <v>91500</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>128472993</v>
       </c>
       <c r="B6" t="n">
-        <v>98646</v>
+        <v>98653</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>128473375</v>
       </c>
       <c r="B7" t="n">
-        <v>100786</v>
+        <v>100793</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 10968-2025 artfynd.xlsx
+++ b/artfynd/A 10968-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128473458</v>
       </c>
       <c r="B2" t="n">
-        <v>91500</v>
+        <v>91504</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>128473328</v>
       </c>
       <c r="B3" t="n">
-        <v>100793</v>
+        <v>100797</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>128473231</v>
       </c>
       <c r="B4" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>128473282</v>
       </c>
       <c r="B5" t="n">
-        <v>91500</v>
+        <v>91504</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>128472993</v>
       </c>
       <c r="B6" t="n">
-        <v>98653</v>
+        <v>98657</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>128473375</v>
       </c>
       <c r="B7" t="n">
-        <v>100793</v>
+        <v>100797</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>128473340</v>
       </c>
       <c r="B8" t="n">
-        <v>82979</v>
+        <v>82983</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 10968-2025 artfynd.xlsx
+++ b/artfynd/A 10968-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128473458</v>
       </c>
       <c r="B2" t="n">
-        <v>91504</v>
+        <v>91509</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>128473328</v>
       </c>
       <c r="B3" t="n">
-        <v>100797</v>
+        <v>100804</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>128473231</v>
       </c>
       <c r="B4" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>128473282</v>
       </c>
       <c r="B5" t="n">
-        <v>91504</v>
+        <v>91509</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>128472993</v>
       </c>
       <c r="B6" t="n">
-        <v>98657</v>
+        <v>98664</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>128473375</v>
       </c>
       <c r="B7" t="n">
-        <v>100797</v>
+        <v>100804</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>128473340</v>
       </c>
       <c r="B8" t="n">
-        <v>82983</v>
+        <v>82892</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
